--- a/Student Attendance/ECE (Deffodils)/ECE (Daffodils) Monthly Attendance - September-2024.xlsx
+++ b/Student Attendance/ECE (Deffodils)/ECE (Daffodils) Monthly Attendance - September-2024.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government High School\Student Attendance\ECE (Deffodils)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Student Attendance\ECE (Deffodils)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8E6D6F-B3DA-4B18-A43D-CA9165D8AE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8EEEFD-857A-426E-B4FA-83B5AC08865E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ECE (Daffodil) (Girls)" sheetId="17" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="132">
   <si>
     <t>S.No</t>
   </si>
@@ -103,9 +103,6 @@
     <t>Year -2024</t>
   </si>
   <si>
-    <t>Monthly Attendence Month of August-2024</t>
-  </si>
-  <si>
     <t>Goverment high school (SJCHS)</t>
   </si>
   <si>
@@ -313,9 +310,6 @@
     <t>Arham</t>
   </si>
   <si>
-    <t>Mujtaba Ahmed</t>
-  </si>
-  <si>
     <t>Qasim Memon</t>
   </si>
   <si>
@@ -434,6 +428,9 @@
   </si>
   <si>
     <t>SUNDAY - SUNDAY - SUNDAY - SUNDAY</t>
+  </si>
+  <si>
+    <t>Monthly Attendence Month of September-2024</t>
   </si>
 </sst>
 </file>
@@ -665,7 +662,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -724,8 +721,11 @@
     <xf numFmtId="17" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -733,20 +733,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -760,7 +754,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -824,16 +818,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -910,6 +894,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1235,97 +1229,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="27"/>
-      <c r="AC1" s="27"/>
-      <c r="AD1" s="27"/>
-      <c r="AE1" s="27"/>
-      <c r="AF1" s="27"/>
-      <c r="AG1" s="27"/>
-      <c r="AH1" s="27"/>
-      <c r="AI1" s="27"/>
+      <c r="A1" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
     </row>
     <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
+      <c r="A2" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="26" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1448,25 +1442,25 @@
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AJ3" s="38" t="s">
+      <c r="AJ3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="38" t="s">
+      <c r="AK3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="AL3" s="29" t="s">
+      <c r="AL3" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="AM3" s="30"/>
+      <c r="AM3" s="32"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
     </row>
     <row r="4" spans="1:41" ht="36" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
       <c r="F4" s="22">
         <v>45536</v>
       </c>
@@ -1557,8 +1551,8 @@
       <c r="AI4" s="22">
         <v>45565</v>
       </c>
-      <c r="AJ4" s="38"/>
-      <c r="AK4" s="38"/>
+      <c r="AJ4" s="30"/>
+      <c r="AK4" s="30"/>
       <c r="AL4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1576,104 +1570,110 @@
         <v>106</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>36</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="34" t="s">
-        <v>130</v>
+      <c r="F5" s="33" t="s">
+        <v>128</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="34" t="s">
-        <v>130</v>
+        <v>32</v>
+      </c>
+      <c r="M5" s="33" t="s">
+        <v>128</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T5" s="34" t="s">
-        <v>130</v>
+        <v>32</v>
+      </c>
+      <c r="T5" s="33" t="s">
+        <v>128</v>
       </c>
       <c r="U5" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V5" s="36" t="s">
-        <v>131</v>
+        <v>31</v>
+      </c>
+      <c r="V5" s="35" t="s">
+        <v>129</v>
       </c>
       <c r="W5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA5" s="34" t="s">
-        <v>130</v>
+        <v>32</v>
+      </c>
+      <c r="AA5" s="33" t="s">
+        <v>128</v>
       </c>
       <c r="AB5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD5" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF5" s="12"/>
-      <c r="AG5" s="12"/>
-      <c r="AH5" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="AI5" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH5" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI5" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ5" s="5">
-        <f>COUNTIF(F5:AI5,"P")</f>
-        <v>20</v>
+        <f t="shared" ref="AJ5:AJ28" si="1">COUNTIF(F5:AI5,"P")</f>
+        <v>23</v>
       </c>
       <c r="AK5" s="5">
-        <f>COUNTIF(F5:AI5,"A")</f>
+        <f t="shared" ref="AK5:AK28" si="2">COUNTIF(F5:AI5,"A")</f>
         <v>1</v>
       </c>
       <c r="AL5" s="5" t="s">
@@ -1695,92 +1695,98 @@
         <v>75</v>
       </c>
       <c r="C6" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>37</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>38</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="35"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M6" s="34"/>
       <c r="N6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T6" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T6" s="34"/>
       <c r="U6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V6" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V6" s="36"/>
       <c r="W6" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="X6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA6" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA6" s="34"/>
       <c r="AB6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF6" s="12"/>
-      <c r="AG6" s="12"/>
-      <c r="AH6" s="35"/>
-      <c r="AI6" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF6" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG6" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH6" s="34"/>
+      <c r="AI6" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ6" s="5">
-        <f>COUNTIF(F6:AI6,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="AK6" s="5">
-        <f>COUNTIF(F6:AI6,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL6" s="5" t="s">
@@ -1800,92 +1806,98 @@
         <v>109</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="35"/>
+      <c r="F7" s="34"/>
       <c r="G7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M7" s="34"/>
       <c r="N7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T7" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T7" s="34"/>
       <c r="U7" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V7" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V7" s="36"/>
       <c r="W7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y7" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA7" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA7" s="34"/>
       <c r="AB7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF7" s="12"/>
-      <c r="AG7" s="12"/>
-      <c r="AH7" s="35"/>
-      <c r="AI7" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH7" s="34"/>
+      <c r="AI7" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ7" s="5">
-        <f>COUNTIF(F7:AI7,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="AK7" s="5">
-        <f>COUNTIF(F7:AI7,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL7" s="3"/>
@@ -1901,100 +1913,106 @@
         <v>49</v>
       </c>
       <c r="C8" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>40</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>41</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="35"/>
+      <c r="F8" s="34"/>
       <c r="G8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="M8" s="34"/>
       <c r="N8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T8" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T8" s="34"/>
       <c r="U8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V8" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V8" s="36"/>
       <c r="W8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Y8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA8" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA8" s="34"/>
       <c r="AB8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
-      <c r="AH8" s="35"/>
-      <c r="AI8" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH8" s="34"/>
+      <c r="AI8" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ8" s="5">
-        <f>COUNTIF(F8:AI8,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="AK8" s="5">
-        <f>COUNTIF(F8:AI8,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AL8" s="29" t="s">
+      <c r="AL8" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="AM8" s="31"/>
-      <c r="AN8" s="31"/>
-      <c r="AO8" s="30"/>
+      <c r="AM8" s="37"/>
+      <c r="AN8" s="37"/>
+      <c r="AO8" s="32"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -2004,91 +2022,99 @@
         <v>104</v>
       </c>
       <c r="C9" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="17" t="s">
         <v>42</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>43</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="35"/>
+      <c r="F9" s="34"/>
       <c r="G9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M9" s="34"/>
       <c r="N9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T9" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T9" s="34"/>
       <c r="U9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V9" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V9" s="36"/>
       <c r="W9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA9" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA9" s="34"/>
       <c r="AB9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD9" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AD9" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AE9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF9" s="12"/>
-      <c r="AG9" s="12"/>
-      <c r="AH9" s="35"/>
-      <c r="AI9" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH9" s="34"/>
+      <c r="AI9" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ9" s="5">
-        <f>COUNTIF(F9:AI9,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="AK9" s="5">
-        <f>COUNTIF(F9:AI9,"A")</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="AL9" s="5" t="s">
         <v>13</v>
@@ -2111,92 +2137,98 @@
         <v>88</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="35"/>
+      <c r="F10" s="34"/>
       <c r="G10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M10" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M10" s="34"/>
       <c r="N10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T10" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T10" s="34"/>
       <c r="U10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V10" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V10" s="36"/>
       <c r="W10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA10" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA10" s="34"/>
       <c r="AB10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF10" s="12"/>
-      <c r="AG10" s="12"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH10" s="34"/>
+      <c r="AI10" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ10" s="5">
-        <f>COUNTIF(F10:AI10,"P")</f>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="AK10" s="5">
-        <f>COUNTIF(F10:AI10,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL10" s="5" t="s">
@@ -2223,106 +2255,114 @@
         <v>59</v>
       </c>
       <c r="C11" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="17" t="s">
         <v>45</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>46</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="35"/>
+      <c r="F11" s="34"/>
       <c r="G11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M11" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M11" s="34"/>
       <c r="N11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T11" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T11" s="34"/>
       <c r="U11" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V11" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V11" s="36"/>
       <c r="W11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA11" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA11" s="34"/>
       <c r="AB11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE11" s="12"/>
-      <c r="AF11" s="12"/>
-      <c r="AG11" s="12"/>
-      <c r="AH11" s="35"/>
-      <c r="AI11" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AE11" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG11" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH11" s="34"/>
+      <c r="AI11" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ11" s="5">
-        <f>COUNTIF(F11:AI11,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
       <c r="AK11" s="5">
-        <f>COUNTIF(F11:AI11,"A")</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="AL11" s="5" t="s">
         <v>18</v>
       </c>
       <c r="AM11" s="13">
         <f>AJ6+AJ7+AJ8+AJ11+AJ12+AJ13+AJ15+AJ19+AJ20+AJ21+AJ22+AJ23+AJ24+AJ25+AJ26+AJ28</f>
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="AN11" s="13">
         <f>AJ5+AJ9+AJ10+AJ14+AJ16+AJ17+AJ18+AJ27</f>
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="AO11" s="13">
         <f>AM11+AN11</f>
-        <v>459</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
@@ -2333,92 +2373,98 @@
         <v>83</v>
       </c>
       <c r="C12" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>47</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>48</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="35"/>
+      <c r="F12" s="34"/>
       <c r="G12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M12" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M12" s="34"/>
       <c r="N12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T12" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T12" s="34"/>
       <c r="U12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V12" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V12" s="36"/>
       <c r="W12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y12" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z12" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA12" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="AA12" s="34"/>
       <c r="AB12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF12" s="12"/>
-      <c r="AG12" s="12"/>
-      <c r="AH12" s="35"/>
-      <c r="AI12" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH12" s="34"/>
+      <c r="AI12" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ12" s="5">
-        <f>COUNTIF(F12:AI12,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="AK12" s="5">
-        <f>COUNTIF(F12:AI12,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL12" s="5" t="s">
@@ -2426,15 +2472,15 @@
       </c>
       <c r="AM12" s="13">
         <f>AM11/AM10</f>
-        <v>0.61740890688259109</v>
+        <v>0.69635627530364375</v>
       </c>
       <c r="AN12" s="13">
         <f>AN11/AN10</f>
-        <v>0.28205128205128205</v>
+        <v>0.31868131868131866</v>
       </c>
       <c r="AO12" s="13">
         <f>AO11/AO10</f>
-        <v>0.44134615384615383</v>
+        <v>0.49807692307692308</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
@@ -2445,91 +2491,97 @@
         <v>89</v>
       </c>
       <c r="C13" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>49</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>50</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="35"/>
+      <c r="F13" s="34"/>
       <c r="G13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M13" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M13" s="34"/>
       <c r="N13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S13" s="12"/>
-      <c r="T13" s="35"/>
+      <c r="T13" s="34"/>
       <c r="U13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V13" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V13" s="36"/>
       <c r="W13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X13" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Y13" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA13" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="AA13" s="34"/>
       <c r="AB13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD13" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE13" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF13" s="12"/>
-      <c r="AG13" s="12"/>
-      <c r="AH13" s="35"/>
-      <c r="AI13" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH13" s="34"/>
+      <c r="AI13" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AJ13" s="5">
-        <f>COUNTIF(F13:AI13,"P")</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="AK13" s="5">
-        <f>COUNTIF(F13:AI13,"A")</f>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
       <c r="AL13" s="3"/>
       <c r="AM13" s="18"/>
@@ -2544,93 +2596,99 @@
         <v>86</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>51</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>52</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="35"/>
+      <c r="F14" s="34"/>
       <c r="G14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M14" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M14" s="34"/>
       <c r="N14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T14" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T14" s="34"/>
       <c r="U14" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V14" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V14" s="36"/>
       <c r="W14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA14" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA14" s="34"/>
       <c r="AB14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD14" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF14" s="12"/>
-      <c r="AG14" s="12"/>
-      <c r="AH14" s="35"/>
-      <c r="AI14" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH14" s="34"/>
+      <c r="AI14" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AJ14" s="5">
-        <f>COUNTIF(F14:AI14,"P")</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="AK14" s="5">
-        <f>COUNTIF(F14:AI14,"A")</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
@@ -2645,92 +2703,98 @@
         <v>105</v>
       </c>
       <c r="C15" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="17" t="s">
         <v>53</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>54</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="35"/>
+      <c r="F15" s="34"/>
       <c r="G15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="34"/>
+      <c r="N15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S15" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="T15" s="34"/>
+      <c r="U15" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="V15" s="36"/>
+      <c r="W15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="X15" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="Y15" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="K15" s="12" t="s">
+      <c r="Z15" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="L15" s="12" t="s">
+      <c r="AA15" s="34"/>
+      <c r="AB15" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="35"/>
-      <c r="N15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="P15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="S15" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="T15" s="35"/>
-      <c r="U15" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="V15" s="37"/>
-      <c r="W15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="X15" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y15" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z15" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="12" t="s">
-        <v>34</v>
-      </c>
       <c r="AC15" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD15" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF15" s="12"/>
-      <c r="AG15" s="12"/>
-      <c r="AH15" s="35"/>
-      <c r="AI15" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH15" s="34"/>
+      <c r="AI15" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ15" s="5">
-        <f>COUNTIF(F15:AI15,"P")</f>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>18</v>
       </c>
       <c r="AK15" s="5">
-        <f>COUNTIF(F15:AI15,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL15" s="3"/>
@@ -2746,100 +2810,106 @@
         <v>107</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="35"/>
+      <c r="F16" s="34"/>
       <c r="G16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="M16" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="M16" s="34"/>
       <c r="N16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T16" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T16" s="34"/>
       <c r="U16" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V16" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V16" s="36"/>
       <c r="W16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA16" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA16" s="34"/>
       <c r="AB16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF16" s="12"/>
-      <c r="AG16" s="12"/>
-      <c r="AH16" s="35"/>
-      <c r="AI16" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH16" s="34"/>
+      <c r="AI16" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ16" s="5">
-        <f>COUNTIF(F16:AI16,"P")</f>
-        <v>17</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="AK16" s="5">
-        <f>COUNTIF(F16:AI16,"A")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AL16" s="29" t="s">
+      <c r="AL16" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="AM16" s="31"/>
-      <c r="AN16" s="31"/>
-      <c r="AO16" s="30"/>
+      <c r="AM16" s="37"/>
+      <c r="AN16" s="37"/>
+      <c r="AO16" s="32"/>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -2849,92 +2919,98 @@
         <v>84</v>
       </c>
       <c r="C17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>56</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>57</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="35"/>
+      <c r="F17" s="34"/>
       <c r="G17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M17" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M17" s="34"/>
       <c r="N17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T17" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T17" s="34"/>
       <c r="U17" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V17" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V17" s="36"/>
       <c r="W17" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="X17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA17" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA17" s="34"/>
       <c r="AB17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD17" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF17" s="12"/>
-      <c r="AG17" s="12"/>
-      <c r="AH17" s="35"/>
-      <c r="AI17" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH17" s="34"/>
+      <c r="AI17" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ17" s="5">
-        <f>COUNTIF(F17:AI17,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="AK17" s="5">
-        <f>COUNTIF(F17:AI17,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="AL17" s="5" t="s">
@@ -2958,91 +3034,97 @@
         <v>85</v>
       </c>
       <c r="C18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="17" t="s">
         <v>58</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>59</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="35"/>
+      <c r="F18" s="34"/>
       <c r="G18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M18" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M18" s="34"/>
       <c r="N18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R18" s="12"/>
       <c r="S18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T18" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T18" s="34"/>
       <c r="U18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V18" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V18" s="36"/>
       <c r="W18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X18" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Y18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA18" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA18" s="34"/>
       <c r="AB18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD18" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF18" s="12"/>
-      <c r="AG18" s="12"/>
-      <c r="AH18" s="35"/>
-      <c r="AI18" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH18" s="34"/>
+      <c r="AI18" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AJ18" s="5">
-        <f>COUNTIF(F18:AI18,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
       <c r="AK18" s="5">
-        <f>COUNTIF(F18:AI18,"A")</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="AL18" s="5" t="s">
         <v>17</v>
@@ -3068,108 +3150,114 @@
         <v>102</v>
       </c>
       <c r="C19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>60</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>61</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="35"/>
+      <c r="F19" s="34"/>
       <c r="G19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M19" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M19" s="34"/>
       <c r="N19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T19" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T19" s="34"/>
       <c r="U19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V19" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V19" s="36"/>
       <c r="W19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA19" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA19" s="34"/>
       <c r="AB19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF19" s="12"/>
-      <c r="AG19" s="12"/>
-      <c r="AH19" s="35"/>
-      <c r="AI19" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG19" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH19" s="34"/>
+      <c r="AI19" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AJ19" s="5">
-        <f>COUNTIF(F19:AI19,"P")</f>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="AK19" s="5">
-        <f>COUNTIF(F19:AI19,"A")</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="AL19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="AM19" s="13">
         <f>AM18-AM11</f>
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="AN19" s="13">
         <f>AN18-AN11</f>
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="AO19" s="13">
         <f>AM19+AN19</f>
-        <v>581</v>
+        <v>522</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
@@ -3180,92 +3268,98 @@
         <v>87</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="35"/>
+      <c r="F20" s="34"/>
       <c r="G20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M20" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M20" s="34"/>
       <c r="N20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T20" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T20" s="34"/>
       <c r="U20" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V20" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V20" s="36"/>
       <c r="W20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA20" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA20" s="34"/>
       <c r="AB20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD20" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF20" s="12"/>
-      <c r="AG20" s="12"/>
-      <c r="AH20" s="35"/>
-      <c r="AI20" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH20" s="34"/>
+      <c r="AI20" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ20" s="5">
-        <f>COUNTIF(F20:AI20,"P")</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK20" s="5">
-        <f>COUNTIF(F20:AI20,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AL20" s="5" t="s">
@@ -3273,15 +3367,15 @@
       </c>
       <c r="AM20" s="21">
         <f>AM19/AM18</f>
-        <v>0.38259109311740891</v>
+        <v>0.30364372469635625</v>
       </c>
       <c r="AN20" s="21">
         <f>AN19/AN18</f>
-        <v>0.71794871794871795</v>
+        <v>0.68131868131868134</v>
       </c>
       <c r="AO20" s="21">
         <f>AO19/AO18</f>
-        <v>0.55865384615384617</v>
+        <v>0.50192307692307692</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
@@ -3292,92 +3386,98 @@
         <v>71</v>
       </c>
       <c r="C21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="17" t="s">
         <v>63</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>64</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="35"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M21" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M21" s="34"/>
       <c r="N21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S21" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T21" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T21" s="34"/>
       <c r="U21" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V21" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V21" s="36"/>
       <c r="W21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z21" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA21" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA21" s="34"/>
       <c r="AB21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE21" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF21" s="12"/>
-      <c r="AG21" s="12"/>
-      <c r="AH21" s="35"/>
-      <c r="AI21" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF21" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG21" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH21" s="34"/>
+      <c r="AI21" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ21" s="5">
-        <f>COUNTIF(F21:AI21,"P")</f>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="AK21" s="5">
-        <f>COUNTIF(F21:AI21,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3389,91 +3489,97 @@
         <v>81</v>
       </c>
       <c r="C22" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="17" t="s">
         <v>65</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>66</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="35"/>
+      <c r="F22" s="34"/>
       <c r="G22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M22" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M22" s="34"/>
       <c r="N22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S22" s="12"/>
-      <c r="T22" s="35"/>
+      <c r="T22" s="34"/>
       <c r="U22" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V22" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V22" s="36"/>
       <c r="W22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z22" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA22" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA22" s="34"/>
       <c r="AB22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE22" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF22" s="12"/>
-      <c r="AG22" s="12"/>
-      <c r="AH22" s="35"/>
-      <c r="AI22" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF22" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG22" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH22" s="34"/>
+      <c r="AI22" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ22" s="5">
-        <f>COUNTIF(F22:AI22,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
       <c r="AK22" s="5">
-        <f>COUNTIF(F22:AI22,"A")</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
@@ -3484,92 +3590,98 @@
         <v>82</v>
       </c>
       <c r="C23" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>67</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>68</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="35"/>
+      <c r="F23" s="34"/>
       <c r="G23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M23" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M23" s="34"/>
       <c r="N23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S23" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T23" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T23" s="34"/>
       <c r="U23" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V23" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V23" s="36"/>
       <c r="W23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z23" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA23" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA23" s="34"/>
       <c r="AB23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE23" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF23" s="12"/>
-      <c r="AG23" s="12"/>
-      <c r="AH23" s="35"/>
-      <c r="AI23" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF23" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG23" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH23" s="34"/>
+      <c r="AI23" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ23" s="5">
-        <f>COUNTIF(F23:AI23,"P")</f>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="AK23" s="5">
-        <f>COUNTIF(F23:AI23,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3581,92 +3693,98 @@
         <v>68</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="35"/>
+      <c r="F24" s="34"/>
       <c r="G24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M24" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M24" s="34"/>
       <c r="N24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S24" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T24" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T24" s="34"/>
       <c r="U24" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V24" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V24" s="36"/>
       <c r="W24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z24" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA24" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA24" s="34"/>
       <c r="AB24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE24" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF24" s="12"/>
-      <c r="AG24" s="12"/>
-      <c r="AH24" s="35"/>
-      <c r="AI24" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF24" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG24" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH24" s="34"/>
+      <c r="AI24" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ24" s="5">
-        <f>COUNTIF(F24:AI24,"P")</f>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="AK24" s="5">
-        <f>COUNTIF(F24:AI24,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3678,92 +3796,98 @@
         <v>69</v>
       </c>
       <c r="C25" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>70</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>71</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="35"/>
+      <c r="F25" s="34"/>
       <c r="G25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M25" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M25" s="34"/>
       <c r="N25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T25" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T25" s="34"/>
       <c r="U25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V25" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V25" s="36"/>
       <c r="W25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA25" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA25" s="34"/>
       <c r="AB25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF25" s="12"/>
-      <c r="AG25" s="12"/>
-      <c r="AH25" s="35"/>
-      <c r="AI25" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF25" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG25" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH25" s="34"/>
+      <c r="AI25" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ25" s="5">
-        <f>COUNTIF(F25:AI25,"P")</f>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="AK25" s="5">
-        <f>COUNTIF(F25:AI25,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3775,92 +3899,98 @@
         <v>70</v>
       </c>
       <c r="C26" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="17" t="s">
         <v>72</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>73</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="35"/>
+      <c r="F26" s="34"/>
       <c r="G26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M26" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M26" s="34"/>
       <c r="N26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S26" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T26" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T26" s="34"/>
       <c r="U26" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V26" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V26" s="36"/>
       <c r="W26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z26" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA26" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA26" s="34"/>
       <c r="AB26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE26" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF26" s="12"/>
-      <c r="AG26" s="12"/>
-      <c r="AH26" s="35"/>
-      <c r="AI26" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF26" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG26" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH26" s="34"/>
+      <c r="AI26" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ26" s="5">
-        <f>COUNTIF(F26:AI26,"P")</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK26" s="5">
-        <f>COUNTIF(F26:AI26,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3872,92 +4002,98 @@
         <v>103</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="35"/>
+      <c r="F27" s="34"/>
       <c r="G27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M27" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M27" s="34"/>
       <c r="N27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T27" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T27" s="34"/>
       <c r="U27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V27" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V27" s="36"/>
       <c r="W27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA27" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA27" s="34"/>
       <c r="AB27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD27" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AE27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF27" s="12"/>
-      <c r="AG27" s="12"/>
-      <c r="AH27" s="35"/>
-      <c r="AI27" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF27" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG27" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH27" s="34"/>
+      <c r="AI27" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ27" s="5">
-        <f>COUNTIF(F27:AI27,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="AK27" s="5">
-        <f>COUNTIF(F27:AI27,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -3969,164 +4105,170 @@
         <v>149</v>
       </c>
       <c r="C28" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" s="17" t="s">
         <v>75</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>76</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="35"/>
+      <c r="F28" s="34"/>
       <c r="G28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="M28" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="M28" s="34"/>
       <c r="N28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="T28" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="T28" s="34"/>
       <c r="U28" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V28" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V28" s="36"/>
       <c r="W28" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="X28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y28" s="12"/>
       <c r="Z28" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA28" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA28" s="34"/>
       <c r="AB28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE28" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF28" s="12"/>
-      <c r="AG28" s="12"/>
-      <c r="AH28" s="35"/>
-      <c r="AI28" s="12"/>
+        <v>31</v>
+      </c>
+      <c r="AF28" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG28" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH28" s="34"/>
+      <c r="AI28" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AJ28" s="5">
-        <f>COUNTIF(F28:AI28,"P")</f>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>16</v>
       </c>
       <c r="AK28" s="5">
-        <f>COUNTIF(F28:AI28,"A")</f>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="AH5:AH28"/>
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="F5:F28"/>
+    <mergeCell ref="M5:M28"/>
+    <mergeCell ref="V5:V28"/>
+    <mergeCell ref="T5:T28"/>
+    <mergeCell ref="AA5:AA28"/>
+    <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="A2:AI2"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AM3"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A1:AI1"/>
-    <mergeCell ref="A2:AI2"/>
-    <mergeCell ref="AJ3:AJ4"/>
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="F5:F28"/>
-    <mergeCell ref="M5:M28"/>
-    <mergeCell ref="V5:V28"/>
-    <mergeCell ref="T5:T28"/>
-    <mergeCell ref="AA5:AA28"/>
-    <mergeCell ref="AH5:AH28"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL16:AO16"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5 M5 T5 V5 AA5 AH5 G5:L28 N5:S28 U5:U28 W5:Z28 AB5:AG28 AI5:AI28 F4:AI4">
-    <cfRule type="expression" dxfId="17" priority="9">
+  <conditionalFormatting sqref="B5:B28">
+    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5 M5 T5 V5 AA5 AH5 G5:L28 N5:S28 U5:U28 W5:Z28 F4:AI4 AB5:AG28 AI5:AI28">
+    <cfRule type="expression" dxfId="16" priority="9">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5 M5 T5 V5 AA5 AH5 G5:L28 N5:S28 U5:U28 W5:Z28 AB5:AG28 AI5:AI28">
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5 M5 T5 V5 AA5 AH5 G5:L28 N5:S28 U5:U28 W5:Z28 AB5:AG28 AL4:AM4 AI5:AI28 F3:AI4">
-    <cfRule type="expression" dxfId="14" priority="10">
+  <conditionalFormatting sqref="F3:AI4 F5 M5 T5 V5 AA5 AH5 G5:L28 N5:S28 U5:U28 W5:Z28 AL4:AM4 AB5:AG28 AI5:AI28">
+    <cfRule type="expression" dxfId="13" priority="10">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ3:AK3 AJ5:AK28">
-    <cfRule type="expression" dxfId="13" priority="11">
+    <cfRule type="expression" dxfId="12" priority="11">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL5:AL6">
-    <cfRule type="expression" dxfId="12" priority="8">
+    <cfRule type="expression" dxfId="11" priority="8">
       <formula>AL$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL9:AL12">
-    <cfRule type="expression" dxfId="11" priority="6">
+    <cfRule type="expression" dxfId="10" priority="6">
       <formula>AL$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL17:AL20">
-    <cfRule type="expression" dxfId="10" priority="5">
+    <cfRule type="expression" dxfId="9" priority="5">
       <formula>AL$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AO9">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="8" priority="7">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM17:AO17">
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>AM$3="Sun"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B28">
-    <cfRule type="duplicateValues" dxfId="7" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4138,7 +4280,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:AO38"/>
+  <dimension ref="A1:AO36"/>
   <sheetFormatPr defaultColWidth="3.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
@@ -4180,1071 +4322,1236 @@
     <col min="42" max="16384" width="3.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="26"/>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
+    <row r="1" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
     </row>
-    <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
+    <row r="2" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
     </row>
-    <row r="3" spans="1:41" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E3" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="str">
-        <f t="shared" ref="F4:AI4" si="0">TEXT(F5,"ddd")</f>
+      <c r="F3" s="2" t="str">
+        <f t="shared" ref="F3:AI3" si="0">TEXT(F4,"ddd")</f>
         <v>Sun</v>
       </c>
-      <c r="G4" s="2" t="str">
+      <c r="G3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="H4" s="2" t="str">
+      <c r="H3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="I4" s="2" t="str">
+      <c r="I3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="J4" s="2" t="str">
+      <c r="J3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="K4" s="2" t="str">
+      <c r="K3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="L4" s="2" t="str">
+      <c r="L3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="M4" s="2" t="str">
+      <c r="M3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="N4" s="2" t="str">
+      <c r="N3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="O4" s="2" t="str">
+      <c r="O3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="P4" s="2" t="str">
+      <c r="P3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="Q4" s="2" t="str">
+      <c r="Q3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="R4" s="2" t="str">
+      <c r="R3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="S4" s="2" t="str">
+      <c r="S3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="T4" s="2" t="str">
+      <c r="T3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="U4" s="2" t="str">
+      <c r="U3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="V4" s="2" t="str">
+      <c r="V3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="W4" s="2" t="str">
+      <c r="W3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="X4" s="2" t="str">
+      <c r="X3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="Y4" s="2" t="str">
+      <c r="Y3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="Z4" s="2" t="str">
+      <c r="Z3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AA4" s="2" t="str">
+      <c r="AA3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="AB4" s="2" t="str">
+      <c r="AB3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AC4" s="2" t="str">
+      <c r="AC3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="AD4" s="2" t="str">
+      <c r="AD3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="AE4" s="2" t="str">
+      <c r="AE3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AF4" s="2" t="str">
+      <c r="AF3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="AG4" s="2" t="str">
+      <c r="AG3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="AH4" s="2" t="str">
+      <c r="AH3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="AI4" s="2" t="str">
+      <c r="AI3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="AJ4" s="38" t="s">
+      <c r="AJ3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="AK4" s="38" t="s">
+      <c r="AK3" s="30" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:41" ht="36" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="22">
+    <row r="4" spans="1:41" ht="36" x14ac:dyDescent="0.25">
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="22">
         <v>45536</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G4" s="22">
         <v>45537</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H4" s="22">
         <v>45538</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I4" s="22">
         <v>45539</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J4" s="22">
         <v>45540</v>
       </c>
-      <c r="K5" s="22">
+      <c r="K4" s="22">
         <v>45541</v>
       </c>
-      <c r="L5" s="22">
+      <c r="L4" s="22">
         <v>45542</v>
       </c>
-      <c r="M5" s="22">
+      <c r="M4" s="22">
         <v>45543</v>
       </c>
-      <c r="N5" s="22">
+      <c r="N4" s="22">
         <v>45544</v>
       </c>
-      <c r="O5" s="22">
+      <c r="O4" s="22">
         <v>45545</v>
       </c>
-      <c r="P5" s="22">
+      <c r="P4" s="22">
         <v>45546</v>
       </c>
-      <c r="Q5" s="22">
+      <c r="Q4" s="22">
         <v>45547</v>
       </c>
-      <c r="R5" s="22">
+      <c r="R4" s="22">
         <v>45548</v>
       </c>
-      <c r="S5" s="22">
+      <c r="S4" s="22">
         <v>45549</v>
       </c>
-      <c r="T5" s="22">
+      <c r="T4" s="22">
         <v>45550</v>
       </c>
-      <c r="U5" s="22">
+      <c r="U4" s="22">
         <v>45551</v>
       </c>
-      <c r="V5" s="22">
+      <c r="V4" s="22">
         <v>45552</v>
       </c>
-      <c r="W5" s="22">
+      <c r="W4" s="22">
         <v>45553</v>
       </c>
-      <c r="X5" s="22">
+      <c r="X4" s="22">
         <v>45554</v>
       </c>
-      <c r="Y5" s="22">
+      <c r="Y4" s="22">
         <v>45555</v>
       </c>
-      <c r="Z5" s="22">
+      <c r="Z4" s="22">
         <v>45556</v>
       </c>
-      <c r="AA5" s="22">
+      <c r="AA4" s="22">
         <v>45557</v>
       </c>
-      <c r="AB5" s="22">
+      <c r="AB4" s="22">
         <v>45558</v>
       </c>
-      <c r="AC5" s="22">
+      <c r="AC4" s="22">
         <v>45559</v>
       </c>
-      <c r="AD5" s="22">
+      <c r="AD4" s="22">
         <v>45560</v>
       </c>
-      <c r="AE5" s="22">
+      <c r="AE4" s="22">
         <v>45561</v>
       </c>
-      <c r="AF5" s="22">
+      <c r="AF4" s="22">
         <v>45562</v>
       </c>
-      <c r="AG5" s="22">
+      <c r="AG4" s="22">
         <v>45563</v>
       </c>
-      <c r="AH5" s="22">
+      <c r="AH4" s="22">
         <v>45564</v>
       </c>
-      <c r="AI5" s="22">
+      <c r="AI4" s="22">
         <v>45565</v>
       </c>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="38"/>
+      <c r="AJ4" s="30"/>
+      <c r="AK4" s="30"/>
     </row>
-    <row r="6" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="5" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B5" s="7">
         <v>61</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="U5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="V5" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="W5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="X5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA5" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH5" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ5" s="5">
+        <f t="shared" ref="AJ5:AJ36" si="1">COUNTIF(F5:AI5,"P")</f>
+        <v>23</v>
+      </c>
+      <c r="AK5" s="5">
+        <f t="shared" ref="AK5:AK36" si="2">COUNTIF(F5:AI5,"A")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="13">
+        <v>2</v>
+      </c>
+      <c r="B6" s="15">
+        <v>79</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="D6" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="34" t="s">
-        <v>132</v>
-      </c>
+      <c r="F6" s="34"/>
       <c r="G6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6" s="34" t="s">
-        <v>132</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="M6" s="34"/>
       <c r="N6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T6" s="34" t="s">
-        <v>132</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="T6" s="34"/>
       <c r="U6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V6" s="36" t="s">
-        <v>131</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="V6" s="36"/>
       <c r="W6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA6" s="34" t="s">
-        <v>132</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="AA6" s="34"/>
       <c r="AB6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD6" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF6" s="12"/>
-      <c r="AG6" s="12"/>
-      <c r="AH6" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="AI6" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF6" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG6" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH6" s="34"/>
+      <c r="AI6" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ6" s="5">
-        <f>COUNTIF(F6:AI6,"P")</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK6" s="5">
-        <f>COUNTIF(F6:AI6,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
+      <c r="AL6" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM6" s="32"/>
+      <c r="AN6" s="3"/>
+      <c r="AO6" s="3"/>
     </row>
-    <row r="7" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="13">
-        <v>2</v>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>3</v>
       </c>
       <c r="B7" s="15">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="35"/>
+      <c r="F7" s="34"/>
       <c r="G7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M7" s="34"/>
       <c r="N7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T7" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T7" s="34"/>
       <c r="U7" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="V7" s="37"/>
+      <c r="V7" s="36"/>
       <c r="W7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA7" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA7" s="34"/>
       <c r="AB7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD7" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF7" s="12"/>
-      <c r="AG7" s="12"/>
-      <c r="AH7" s="35"/>
-      <c r="AI7" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH7" s="34"/>
+      <c r="AI7" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ7" s="5">
-        <f>COUNTIF(F7:AI7,"P")</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK7" s="5">
-        <f>COUNTIF(F7:AI7,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AL7" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="AM7" s="30"/>
+      <c r="AL7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM7" s="5">
+        <v>31</v>
+      </c>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>3</v>
+      <c r="A8" s="13">
+        <v>4</v>
       </c>
       <c r="B8" s="15">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="35"/>
+      <c r="F8" s="34"/>
       <c r="G8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="M8" s="34"/>
       <c r="N8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R8" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T8" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T8" s="34"/>
       <c r="U8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V8" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V8" s="36"/>
       <c r="W8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Y8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA8" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA8" s="34"/>
       <c r="AB8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD8" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
-      <c r="AH8" s="35"/>
-      <c r="AI8" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH8" s="34"/>
+      <c r="AI8" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ8" s="5">
-        <f>COUNTIF(F8:AI8,"P")</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
       <c r="AK8" s="5">
-        <f>COUNTIF(F8:AI8,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="AL8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM8" s="5">
-        <v>31</v>
-      </c>
-      <c r="AN8" s="3"/>
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AL8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM8" s="13">
+        <v>26</v>
+      </c>
+      <c r="AN8" s="14" t="s">
+        <v>10</v>
+      </c>
       <c r="AO8" s="3"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A9" s="13">
-        <v>4</v>
+      <c r="A9" s="6">
+        <v>5</v>
       </c>
       <c r="B9" s="15">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="35"/>
+      <c r="F9" s="34"/>
       <c r="G9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L9" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M9" s="35"/>
+      <c r="M9" s="34"/>
       <c r="N9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R9" s="12" t="s">
         <v>32</v>
       </c>
       <c r="S9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T9" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T9" s="34"/>
       <c r="U9" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="V9" s="37"/>
+      <c r="V9" s="36"/>
       <c r="W9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X9" s="12" t="s">
         <v>32</v>
       </c>
       <c r="Y9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA9" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA9" s="34"/>
       <c r="AB9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF9" s="12"/>
-      <c r="AG9" s="12"/>
-      <c r="AH9" s="35"/>
-      <c r="AI9" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH9" s="34"/>
+      <c r="AI9" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ9" s="5">
-        <f>COUNTIF(F9:AI9,"P")</f>
-        <v>17</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK9" s="5">
-        <f>COUNTIF(F9:AI9,"A")</f>
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AL9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM9" s="13">
         <v>4</v>
       </c>
-      <c r="AL9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM9" s="13">
-        <v>26</v>
-      </c>
-      <c r="AN9" s="14" t="s">
-        <v>10</v>
-      </c>
+      <c r="AN9" s="3"/>
       <c r="AO9" s="3"/>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>5</v>
+      <c r="A10" s="13">
+        <v>6</v>
       </c>
       <c r="B10" s="15">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="35"/>
+      <c r="F10" s="34"/>
       <c r="G10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K10" s="12" t="s">
         <v>32</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M10" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M10" s="34"/>
       <c r="N10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T10" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T10" s="34"/>
       <c r="U10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V10" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V10" s="36"/>
       <c r="W10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA10" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA10" s="34"/>
       <c r="AB10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF10" s="12"/>
-      <c r="AG10" s="12"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH10" s="34"/>
+      <c r="AI10" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ10" s="5">
-        <f>COUNTIF(F10:AI10,"P")</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="AK10" s="5">
-        <f>COUNTIF(F10:AI10,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="AL10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AM10" s="13">
-        <v>4</v>
-      </c>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
       <c r="AO10" s="3"/>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
-        <v>6</v>
+    <row r="11" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>7</v>
       </c>
       <c r="B11" s="15">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="35"/>
+      <c r="F11" s="34"/>
       <c r="G11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M11" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M11" s="34"/>
       <c r="N11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T11" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T11" s="34"/>
       <c r="U11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V11" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V11" s="36"/>
       <c r="W11" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="X11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA11" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="AA11" s="34"/>
       <c r="AB11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD11" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF11" s="12"/>
-      <c r="AG11" s="12"/>
-      <c r="AH11" s="35"/>
-      <c r="AI11" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF11" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH11" s="34"/>
+      <c r="AI11" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ11" s="5">
-        <f>COUNTIF(F11:AI11,"P")</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="AK11" s="5">
-        <f>COUNTIF(F11:AI11,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
-      <c r="AO11" s="3"/>
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="AL11" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM11" s="24"/>
+      <c r="AN11" s="24"/>
+      <c r="AO11" s="25"/>
     </row>
-    <row r="12" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
-        <v>7</v>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A12" s="13">
+        <v>8</v>
       </c>
       <c r="B12" s="15">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="35"/>
+      <c r="F12" s="34"/>
       <c r="G12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M12" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M12" s="34"/>
       <c r="N12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T12" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T12" s="34"/>
       <c r="U12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V12" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V12" s="36"/>
       <c r="W12" s="12" t="s">
         <v>32</v>
       </c>
       <c r="X12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z12" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA12" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="AA12" s="34"/>
       <c r="AB12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD12" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF12" s="12"/>
-      <c r="AG12" s="12"/>
-      <c r="AH12" s="35"/>
-      <c r="AI12" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH12" s="34"/>
+      <c r="AI12" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ12" s="5">
-        <f>COUNTIF(F12:AI12,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="AK12" s="5">
-        <f>COUNTIF(F12:AI12,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AL12" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="AM12" s="24"/>
-      <c r="AN12" s="24"/>
-      <c r="AO12" s="25"/>
+      <c r="AL12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM12" s="13">
+        <f>19*26</f>
+        <v>494</v>
+      </c>
+      <c r="AN12" s="13">
+        <f>21*26</f>
+        <v>546</v>
+      </c>
+      <c r="AO12" s="13">
+        <f>SUM(AM12:AN12)</f>
+        <v>1040</v>
+      </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A13" s="13">
-        <v>8</v>
+      <c r="A13" s="6">
+        <v>9</v>
       </c>
       <c r="B13" s="15">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="35"/>
+      <c r="F13" s="34"/>
       <c r="G13" s="12" t="s">
         <v>32</v>
       </c>
@@ -5263,7 +5570,7 @@
       <c r="L13" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M13" s="35"/>
+      <c r="M13" s="34"/>
       <c r="N13" s="12" t="s">
         <v>32</v>
       </c>
@@ -5282,11 +5589,11 @@
       <c r="S13" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="T13" s="35"/>
+      <c r="T13" s="34"/>
       <c r="U13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V13" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V13" s="36"/>
       <c r="W13" s="12" t="s">
         <v>32</v>
       </c>
@@ -5297,9 +5604,9 @@
         <v>32</v>
       </c>
       <c r="Z13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA13" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="AA13" s="34"/>
       <c r="AB13" s="12" t="s">
         <v>32</v>
       </c>
@@ -5312,899 +5619,956 @@
       <c r="AE13" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AF13" s="12"/>
-      <c r="AG13" s="12"/>
-      <c r="AH13" s="35"/>
-      <c r="AI13" s="12"/>
+      <c r="AF13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH13" s="34"/>
+      <c r="AI13" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ13" s="5">
-        <f>COUNTIF(F13:AI13,"P")</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="AK13" s="5">
-        <f>COUNTIF(F13:AI13,"A")</f>
-        <v>21</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AM13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AN13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO13" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="AM13" s="13">
+        <f>AJ7+AJ17</f>
+        <v>46</v>
+      </c>
+      <c r="AN13" s="13" t="e">
+        <f>AJ5+AJ6+AJ8+AJ9+AJ10+AJ11+#REF!+AJ12+AJ13+AJ14+AJ15+AJ16+AJ18+AJ19</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AO13" s="13" t="e">
+        <f>AM13+AN13</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
-        <v>9</v>
+      <c r="A14" s="13">
+        <v>10</v>
       </c>
       <c r="B14" s="15">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="35"/>
+      <c r="F14" s="34"/>
       <c r="G14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" s="34"/>
+      <c r="N14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T14" s="34"/>
+      <c r="U14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="V14" s="36"/>
+      <c r="W14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="X14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA14" s="34"/>
+      <c r="AB14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH14" s="34"/>
+      <c r="AI14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ14" s="5">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="AK14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM14" s="13">
+        <f>AM13/AM12</f>
+        <v>9.3117408906882596E-2</v>
+      </c>
+      <c r="AN14" s="13" t="e">
+        <f>AN13/AN12</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AO14" s="13" t="e">
+        <f>AO13/AO12</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>11</v>
+      </c>
+      <c r="B15" s="15">
+        <v>100</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="34"/>
+      <c r="G15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="34"/>
+      <c r="N15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="S15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" s="34"/>
+      <c r="U15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="V15" s="36"/>
+      <c r="W15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="X15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA15" s="34"/>
+      <c r="AB15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH15" s="34"/>
+      <c r="AI15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ15" s="5">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="AK15" s="5">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AL15" s="3"/>
+      <c r="AM15" s="18"/>
+      <c r="AN15" s="18"/>
+      <c r="AO15" s="18"/>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A16" s="13">
+        <v>12</v>
+      </c>
+      <c r="B16" s="15">
+        <v>90</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" s="34"/>
+      <c r="N16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T16" s="34"/>
+      <c r="U16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="V16" s="36"/>
+      <c r="W16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="X16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA16" s="34"/>
+      <c r="AB16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH16" s="34"/>
+      <c r="AI16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ16" s="5">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="AK16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL16" s="20"/>
+      <c r="AM16" s="20"/>
+      <c r="AN16" s="20"/>
+      <c r="AO16" s="20"/>
+    </row>
+    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>13</v>
+      </c>
+      <c r="B17" s="15">
+        <v>73</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="34"/>
+      <c r="G17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" s="34"/>
+      <c r="N17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T17" s="34"/>
+      <c r="U17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="V17" s="36"/>
+      <c r="W17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="X17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA17" s="34"/>
+      <c r="AB17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG17" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH17" s="34"/>
+      <c r="AI17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ17" s="5">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="AK17" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AL17" s="3"/>
+      <c r="AM17" s="3"/>
+      <c r="AN17" s="3"/>
+      <c r="AO17" s="3"/>
+    </row>
+    <row r="18" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="13">
+        <v>14</v>
+      </c>
+      <c r="B18" s="15">
+        <v>72</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="34"/>
+      <c r="G18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" s="34"/>
+      <c r="N18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T18" s="34"/>
+      <c r="U18" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="V18" s="36"/>
+      <c r="W18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="X18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA18" s="34"/>
+      <c r="AB18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH18" s="34"/>
+      <c r="AI18" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ18" s="5">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="AK18" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AL18" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM18" s="24"/>
+      <c r="AN18" s="24"/>
+      <c r="AO18" s="25"/>
+    </row>
+    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>15</v>
+      </c>
+      <c r="B19" s="15">
+        <v>74</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="34"/>
+      <c r="G19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="M19" s="34"/>
+      <c r="N19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T19" s="34"/>
+      <c r="U19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="V19" s="36"/>
+      <c r="W19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="X19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z19" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA19" s="34"/>
+      <c r="AB19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG19" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH19" s="34"/>
+      <c r="AI19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ19" s="5">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="AK19" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AL19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO19" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A20" s="13">
+        <v>16</v>
+      </c>
+      <c r="B20" s="15">
+        <v>77</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="34"/>
+      <c r="G20" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="M20" s="34"/>
+      <c r="N20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T20" s="34"/>
+      <c r="U20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="V20" s="36"/>
+      <c r="W20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="X20" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y20" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="Z20" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="AA20" s="34"/>
+      <c r="AB20" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M14" s="35"/>
-      <c r="N14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="P14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="S14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T14" s="35"/>
-      <c r="U14" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V14" s="37"/>
-      <c r="W14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="X14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z14" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA14" s="35"/>
-      <c r="AB14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE14" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF14" s="12"/>
-      <c r="AG14" s="12"/>
-      <c r="AH14" s="35"/>
-      <c r="AI14" s="12"/>
-      <c r="AJ14" s="5">
-        <f>COUNTIF(F14:AI14,"P")</f>
-        <v>19</v>
-      </c>
-      <c r="AK14" s="5">
-        <f>COUNTIF(F14:AI14,"A")</f>
-        <v>2</v>
-      </c>
-      <c r="AL14" s="5" t="s">
+      <c r="AC20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH20" s="34"/>
+      <c r="AI20" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ20" s="5">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="AK20" s="5">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="AL20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AM14" s="13">
+      <c r="AM20" s="13">
         <f>19*26</f>
         <v>494</v>
       </c>
-      <c r="AN14" s="13">
+      <c r="AN20" s="13">
         <f>21*26</f>
         <v>546</v>
       </c>
-      <c r="AO14" s="13">
-        <f>SUM(AM14:AN14)</f>
+      <c r="AO20" s="13">
+        <f>AM20+AN20</f>
         <v>1040</v>
       </c>
-    </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A15" s="13">
-        <v>10</v>
-      </c>
-      <c r="B15" s="15">
-        <v>131</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="35"/>
-      <c r="G15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M15" s="35"/>
-      <c r="N15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="P15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="S15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T15" s="35"/>
-      <c r="U15" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V15" s="37"/>
-      <c r="W15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="X15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z15" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF15" s="12"/>
-      <c r="AG15" s="12"/>
-      <c r="AH15" s="35"/>
-      <c r="AI15" s="12"/>
-      <c r="AJ15" s="5">
-        <f>COUNTIF(F15:AI15,"P")</f>
-        <v>19</v>
-      </c>
-      <c r="AK15" s="5">
-        <f>COUNTIF(F15:AI15,"A")</f>
-        <v>2</v>
-      </c>
-      <c r="AL15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AM15" s="13">
-        <f>AJ8+AJ19</f>
-        <v>41</v>
-      </c>
-      <c r="AN15" s="13">
-        <f>AJ6+AJ7+AJ9+AJ10+AJ11+AJ12+AJ13+AJ14+AJ15+AJ16+AJ17+AJ18+AJ20+AJ21</f>
-        <v>253</v>
-      </c>
-      <c r="AO15" s="13">
-        <f>AM15+AN15</f>
-        <v>294</v>
-      </c>
-    </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
-        <v>11</v>
-      </c>
-      <c r="B16" s="15">
-        <v>101</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="35"/>
-      <c r="G16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M16" s="35"/>
-      <c r="N16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="P16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="S16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T16" s="35"/>
-      <c r="U16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V16" s="37"/>
-      <c r="W16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="X16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF16" s="12"/>
-      <c r="AG16" s="12"/>
-      <c r="AH16" s="35"/>
-      <c r="AI16" s="12"/>
-      <c r="AJ16" s="5">
-        <f>COUNTIF(F16:AI16,"P")</f>
-        <v>21</v>
-      </c>
-      <c r="AK16" s="5">
-        <f>COUNTIF(F16:AI16,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="AL16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM16" s="13">
-        <f>AM15/AM14</f>
-        <v>8.2995951417004055E-2</v>
-      </c>
-      <c r="AN16" s="13">
-        <f>AN15/AN14</f>
-        <v>0.46336996336996339</v>
-      </c>
-      <c r="AO16" s="13">
-        <f>AO15/AO14</f>
-        <v>0.28269230769230769</v>
-      </c>
-    </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A17" s="13">
-        <v>12</v>
-      </c>
-      <c r="B17" s="15">
-        <v>100</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="35"/>
-      <c r="G17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M17" s="35"/>
-      <c r="N17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="P17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R17" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="S17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T17" s="35"/>
-      <c r="U17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V17" s="37"/>
-      <c r="W17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="X17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA17" s="35"/>
-      <c r="AB17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD17" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF17" s="12"/>
-      <c r="AG17" s="12"/>
-      <c r="AH17" s="35"/>
-      <c r="AI17" s="12"/>
-      <c r="AJ17" s="5">
-        <f>COUNTIF(F17:AI17,"P")</f>
-        <v>18</v>
-      </c>
-      <c r="AK17" s="5">
-        <f>COUNTIF(F17:AI17,"A")</f>
-        <v>3</v>
-      </c>
-      <c r="AL17" s="3"/>
-      <c r="AM17" s="18"/>
-      <c r="AN17" s="18"/>
-      <c r="AO17" s="18"/>
-    </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
-        <v>13</v>
-      </c>
-      <c r="B18" s="15">
-        <v>90</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="35"/>
-      <c r="G18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="L18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M18" s="35"/>
-      <c r="N18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="P18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="S18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T18" s="35"/>
-      <c r="U18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V18" s="37"/>
-      <c r="W18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="X18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA18" s="35"/>
-      <c r="AB18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE18" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF18" s="12"/>
-      <c r="AG18" s="12"/>
-      <c r="AH18" s="35"/>
-      <c r="AI18" s="12"/>
-      <c r="AJ18" s="5">
-        <f>COUNTIF(F18:AI18,"P")</f>
-        <v>21</v>
-      </c>
-      <c r="AK18" s="5">
-        <f>COUNTIF(F18:AI18,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="AL18" s="20"/>
-      <c r="AM18" s="20"/>
-      <c r="AN18" s="20"/>
-      <c r="AO18" s="20"/>
-    </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A19" s="13">
-        <v>14</v>
-      </c>
-      <c r="B19" s="15">
-        <v>73</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="35"/>
-      <c r="G19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="L19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M19" s="35"/>
-      <c r="N19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="P19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="S19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T19" s="35"/>
-      <c r="U19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V19" s="37"/>
-      <c r="W19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="X19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA19" s="35"/>
-      <c r="AB19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE19" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF19" s="12"/>
-      <c r="AG19" s="12"/>
-      <c r="AH19" s="35"/>
-      <c r="AI19" s="12"/>
-      <c r="AJ19" s="5">
-        <f>COUNTIF(F19:AI19,"P")</f>
-        <v>21</v>
-      </c>
-      <c r="AK19" s="5">
-        <f>COUNTIF(F19:AI19,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="AL19" s="3"/>
-      <c r="AM19" s="3"/>
-      <c r="AN19" s="3"/>
-      <c r="AO19" s="3"/>
-    </row>
-    <row r="20" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>15</v>
-      </c>
-      <c r="B20" s="15">
-        <v>72</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="35"/>
-      <c r="G20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M20" s="35"/>
-      <c r="N20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="P20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="S20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T20" s="35"/>
-      <c r="U20" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V20" s="37"/>
-      <c r="W20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="X20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA20" s="35"/>
-      <c r="AB20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF20" s="12"/>
-      <c r="AG20" s="12"/>
-      <c r="AH20" s="35"/>
-      <c r="AI20" s="12"/>
-      <c r="AJ20" s="5">
-        <f>COUNTIF(F20:AI20,"P")</f>
-        <v>20</v>
-      </c>
-      <c r="AK20" s="5">
-        <f>COUNTIF(F20:AI20,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="AL20" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM20" s="24"/>
-      <c r="AN20" s="24"/>
-      <c r="AO20" s="25"/>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A21" s="13">
-        <v>16</v>
+      <c r="A21" s="6">
+        <v>17</v>
       </c>
       <c r="B21" s="15">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="35"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="M21" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="M21" s="34"/>
       <c r="N21" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S21" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T21" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T21" s="34"/>
       <c r="U21" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V21" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="V21" s="36"/>
       <c r="W21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z21" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA21" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="AA21" s="34"/>
       <c r="AB21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD21" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE21" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF21" s="12"/>
-      <c r="AG21" s="12"/>
-      <c r="AH21" s="35"/>
-      <c r="AI21" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF21" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG21" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH21" s="34"/>
+      <c r="AI21" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ21" s="5">
-        <f>COUNTIF(F21:AI21,"P")</f>
-        <v>18</v>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
       <c r="AK21" s="5">
-        <f>COUNTIF(F21:AI21,"A")</f>
-        <v>3</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="AL21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AM21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AN21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO21" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="AM21" s="13">
+        <f>AM20-AM13</f>
+        <v>448</v>
+      </c>
+      <c r="AN21" s="13" t="e">
+        <f>AN20-AN13</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AO21" s="13" t="e">
+        <f>AM21+AN21</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
-        <v>17</v>
+      <c r="A22" s="13">
+        <v>18</v>
       </c>
       <c r="B22" s="15">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="35"/>
+      <c r="F22" s="34"/>
       <c r="G22" s="12" t="s">
         <v>32</v>
       </c>
@@ -6223,119 +6587,125 @@
       <c r="L22" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M22" s="35"/>
+      <c r="M22" s="34"/>
       <c r="N22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S22" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T22" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T22" s="34"/>
       <c r="U22" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V22" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V22" s="36"/>
       <c r="W22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X22" s="12" t="s">
         <v>32</v>
       </c>
       <c r="Y22" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z22" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA22" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="AA22" s="34"/>
       <c r="AB22" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD22" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE22" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF22" s="12"/>
-      <c r="AG22" s="12"/>
-      <c r="AH22" s="35"/>
-      <c r="AI22" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF22" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG22" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH22" s="34"/>
+      <c r="AI22" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ22" s="5">
-        <f>COUNTIF(F22:AI22,"P")</f>
-        <v>11</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK22" s="5">
-        <f>COUNTIF(F22:AI22,"A")</f>
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="AL22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM22" s="13">
-        <f>19*26</f>
-        <v>494</v>
-      </c>
-      <c r="AN22" s="13">
-        <f>21*26</f>
-        <v>546</v>
-      </c>
-      <c r="AO22" s="13">
-        <f>AM22+AN22</f>
-        <v>1040</v>
+        <v>16</v>
+      </c>
+      <c r="AM22" s="21">
+        <f>AM21/AM20</f>
+        <v>0.90688259109311742</v>
+      </c>
+      <c r="AN22" s="21" t="e">
+        <f>AN21/AN20</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AO22" s="21" t="e">
+        <f>AO21/AO20</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A23" s="13">
-        <v>18</v>
+      <c r="A23" s="6">
+        <v>19</v>
       </c>
       <c r="B23" s="15">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="35"/>
+      <c r="F23" s="34"/>
       <c r="G23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L23" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M23" s="35"/>
+      <c r="M23" s="34"/>
       <c r="N23" s="12" t="s">
         <v>32</v>
       </c>
@@ -6343,913 +6713,933 @@
         <v>32</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S23" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T23" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T23" s="34"/>
       <c r="U23" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="V23" s="37"/>
+      <c r="V23" s="36"/>
       <c r="W23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z23" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AA23" s="35"/>
+      <c r="AA23" s="34"/>
       <c r="AB23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD23" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE23" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF23" s="12"/>
-      <c r="AG23" s="12"/>
-      <c r="AH23" s="35"/>
-      <c r="AI23" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF23" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG23" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH23" s="34"/>
+      <c r="AI23" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ23" s="5">
-        <f>COUNTIF(F23:AI23,"P")</f>
-        <v>16</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="AK23" s="5">
-        <f>COUNTIF(F23:AI23,"A")</f>
-        <v>5</v>
-      </c>
-      <c r="AL23" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AM23" s="13">
-        <f>AM22-AM15</f>
-        <v>453</v>
-      </c>
-      <c r="AN23" s="13">
-        <f>AN22-AN15</f>
-        <v>293</v>
-      </c>
-      <c r="AO23" s="13">
-        <f>AM23+AN23</f>
-        <v>746</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>19</v>
+      <c r="A24" s="13">
+        <v>20</v>
       </c>
       <c r="B24" s="15">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="35"/>
+      <c r="F24" s="34"/>
       <c r="G24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M24" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M24" s="34"/>
       <c r="N24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S24" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T24" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T24" s="34"/>
       <c r="U24" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V24" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V24" s="36"/>
       <c r="W24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y24" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Z24" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AA24" s="35"/>
+      <c r="AA24" s="34"/>
       <c r="AB24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD24" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE24" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF24" s="12"/>
-      <c r="AG24" s="12"/>
-      <c r="AH24" s="35"/>
-      <c r="AI24" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF24" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG24" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH24" s="34"/>
+      <c r="AI24" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ24" s="5">
-        <f>COUNTIF(F24:AI24,"P")</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK24" s="5">
-        <f>COUNTIF(F24:AI24,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
-      </c>
-      <c r="AL24" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM24" s="21">
-        <f>AM23/AM22</f>
-        <v>0.917004048582996</v>
-      </c>
-      <c r="AN24" s="21">
-        <f>AN23/AN22</f>
-        <v>0.53663003663003661</v>
-      </c>
-      <c r="AO24" s="21">
-        <f>AO23/AO22</f>
-        <v>0.71730769230769231</v>
       </c>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A25" s="13">
-        <v>20</v>
+      <c r="A25" s="6">
+        <v>21</v>
       </c>
       <c r="B25" s="15">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C25" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>113</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>25</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="35"/>
+      <c r="F25" s="34"/>
       <c r="G25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M25" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M25" s="34"/>
       <c r="N25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T25" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T25" s="34"/>
       <c r="U25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V25" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V25" s="36"/>
       <c r="W25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA25" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA25" s="34"/>
       <c r="AB25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD25" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF25" s="12"/>
-      <c r="AG25" s="12"/>
-      <c r="AH25" s="35"/>
-      <c r="AI25" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF25" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG25" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH25" s="34"/>
+      <c r="AI25" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ25" s="5">
-        <f>COUNTIF(F25:AI25,"P")</f>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="AK25" s="5">
-        <f>COUNTIF(F25:AI25,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
-        <v>21</v>
+      <c r="A26" s="13">
+        <v>22</v>
       </c>
       <c r="B26" s="15">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="35"/>
+      <c r="F26" s="34"/>
       <c r="G26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M26" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M26" s="34"/>
       <c r="N26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S26" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T26" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T26" s="34"/>
       <c r="U26" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V26" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V26" s="36"/>
       <c r="W26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y26" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z26" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA26" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA26" s="34"/>
       <c r="AB26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD26" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE26" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF26" s="12"/>
-      <c r="AG26" s="12"/>
-      <c r="AH26" s="35"/>
-      <c r="AI26" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF26" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG26" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH26" s="34"/>
+      <c r="AI26" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ26" s="5">
-        <f>COUNTIF(F26:AI26,"P")</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK26" s="5">
-        <f>COUNTIF(F26:AI26,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A27" s="13">
-        <v>22</v>
+      <c r="A27" s="6">
+        <v>23</v>
       </c>
       <c r="B27" s="15">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="35"/>
+      <c r="F27" s="34"/>
       <c r="G27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M27" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M27" s="34"/>
       <c r="N27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T27" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T27" s="34"/>
       <c r="U27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V27" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V27" s="36"/>
       <c r="W27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA27" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA27" s="34"/>
       <c r="AB27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD27" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF27" s="12"/>
-      <c r="AG27" s="12"/>
-      <c r="AH27" s="35"/>
-      <c r="AI27" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF27" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG27" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH27" s="34"/>
+      <c r="AI27" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ27" s="5">
-        <f>COUNTIF(F27:AI27,"P")</f>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="AK27" s="5">
-        <f>COUNTIF(F27:AI27,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
-        <v>23</v>
+      <c r="A28" s="13">
+        <v>24</v>
       </c>
       <c r="B28" s="15">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="35"/>
+      <c r="F28" s="34"/>
       <c r="G28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M28" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M28" s="34"/>
       <c r="N28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T28" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T28" s="34"/>
       <c r="U28" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V28" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V28" s="36"/>
       <c r="W28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y28" s="12" t="s">
         <v>32</v>
       </c>
       <c r="Z28" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA28" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA28" s="34"/>
       <c r="AB28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD28" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE28" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF28" s="12"/>
-      <c r="AG28" s="12"/>
-      <c r="AH28" s="35"/>
-      <c r="AI28" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF28" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG28" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH28" s="34"/>
+      <c r="AI28" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ28" s="5">
-        <f>COUNTIF(F28:AI28,"P")</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK28" s="5">
-        <f>COUNTIF(F28:AI28,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A29" s="13">
-        <v>24</v>
+      <c r="A29" s="6">
+        <v>25</v>
       </c>
       <c r="B29" s="15">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C29" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="17" t="s">
         <v>119</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>27</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="35"/>
+      <c r="F29" s="34"/>
       <c r="G29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M29" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M29" s="34"/>
       <c r="N29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T29" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T29" s="34"/>
       <c r="U29" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V29" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V29" s="36"/>
       <c r="W29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z29" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA29" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA29" s="34"/>
       <c r="AB29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD29" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE29" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF29" s="12"/>
-      <c r="AG29" s="12"/>
-      <c r="AH29" s="35"/>
-      <c r="AI29" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF29" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG29" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH29" s="34"/>
+      <c r="AI29" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ29" s="5">
-        <f>COUNTIF(F29:AI29,"P")</f>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="AK29" s="5">
-        <f>COUNTIF(F29:AI29,"A")</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
-        <v>25</v>
+      <c r="A30" s="13">
+        <v>26</v>
       </c>
       <c r="B30" s="15">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="35"/>
+      <c r="F30" s="34"/>
       <c r="G30" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M30" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M30" s="34"/>
       <c r="N30" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P30" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R30" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T30" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="T30" s="34"/>
       <c r="U30" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V30" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V30" s="36"/>
       <c r="W30" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X30" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y30" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z30" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA30" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA30" s="34"/>
       <c r="AB30" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC30" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD30" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE30" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF30" s="12"/>
-      <c r="AG30" s="12"/>
-      <c r="AH30" s="35"/>
-      <c r="AI30" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF30" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG30" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH30" s="34"/>
+      <c r="AI30" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ30" s="5">
-        <f>COUNTIF(F30:AI30,"P")</f>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
       <c r="AK30" s="5">
-        <f>COUNTIF(F30:AI30,"A")</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A31" s="13">
-        <v>26</v>
+      <c r="A31" s="6">
+        <v>27</v>
       </c>
       <c r="B31" s="15">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="C31" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="17" t="s">
         <v>122</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>121</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="35"/>
+      <c r="F31" s="34"/>
       <c r="G31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M31" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M31" s="34"/>
       <c r="N31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R31" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S31" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T31" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="T31" s="34"/>
       <c r="U31" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V31" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V31" s="36"/>
       <c r="W31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z31" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA31" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="AA31" s="34"/>
       <c r="AB31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD31" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE31" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF31" s="12"/>
-      <c r="AG31" s="12"/>
-      <c r="AH31" s="35"/>
-      <c r="AI31" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF31" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG31" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH31" s="34"/>
+      <c r="AI31" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ31" s="5">
-        <f>COUNTIF(F31:AI31,"P")</f>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
       <c r="AK31" s="5">
-        <f>COUNTIF(F31:AI31,"A")</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>27</v>
-      </c>
-      <c r="B32" s="15">
-        <v>141</v>
-      </c>
+      <c r="A32" s="13">
+        <v>28</v>
+      </c>
+      <c r="B32" s="15"/>
       <c r="C32" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" s="17" t="s">
         <v>124</v>
       </c>
+      <c r="D32" s="17"/>
       <c r="E32" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="35"/>
+      <c r="F32" s="34"/>
       <c r="G32" s="12" t="s">
         <v>32</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I32" s="12" t="s">
         <v>32</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M32" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M32" s="34"/>
       <c r="N32" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O32" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P32" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q32" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R32" s="12" t="s">
         <v>32</v>
@@ -7257,96 +7647,98 @@
       <c r="S32" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="T32" s="35"/>
+      <c r="T32" s="34"/>
       <c r="U32" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V32" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V32" s="36"/>
       <c r="W32" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X32" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y32" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z32" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA32" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="AA32" s="34"/>
       <c r="AB32" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC32" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD32" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE32" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF32" s="12"/>
-      <c r="AG32" s="12"/>
-      <c r="AH32" s="35"/>
-      <c r="AI32" s="12"/>
+        <v>31</v>
+      </c>
+      <c r="AF32" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG32" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH32" s="34"/>
+      <c r="AI32" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ32" s="5">
-        <f>COUNTIF(F32:AI32,"P")</f>
-        <v>17</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="AK32" s="5">
-        <f>COUNTIF(F32:AI32,"A")</f>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A33" s="13">
-        <v>28</v>
-      </c>
-      <c r="B33" s="15">
-        <v>140</v>
-      </c>
+      <c r="A33" s="6">
+        <v>29</v>
+      </c>
+      <c r="B33" s="15"/>
       <c r="C33" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="D33" s="17" t="s">
-        <v>124</v>
-      </c>
+      <c r="D33" s="17"/>
       <c r="E33" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="35"/>
+      <c r="F33" s="34"/>
       <c r="G33" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I33" s="12" t="s">
         <v>32</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M33" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M33" s="34"/>
       <c r="N33" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O33" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P33" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R33" s="12" t="s">
         <v>32</v>
@@ -7354,176 +7746,168 @@
       <c r="S33" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="T33" s="35"/>
+      <c r="T33" s="34"/>
       <c r="U33" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V33" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V33" s="36"/>
       <c r="W33" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X33" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y33" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z33" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AA33" s="35"/>
+      <c r="AA33" s="34"/>
       <c r="AB33" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC33" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD33" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE33" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF33" s="12"/>
-      <c r="AG33" s="12"/>
-      <c r="AH33" s="35"/>
-      <c r="AI33" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF33" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG33" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH33" s="34"/>
+      <c r="AI33" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ33" s="5">
-        <f>COUNTIF(F33:AI33,"P")</f>
-        <v>17</v>
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
       <c r="AK33" s="5">
-        <f>COUNTIF(F33:AI33,"A")</f>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>29</v>
+      <c r="A34" s="13">
+        <v>30</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="17"/>
+      <c r="D34" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E34" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="35"/>
-      <c r="G34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="L34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M34" s="35"/>
-      <c r="N34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="P34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q34" s="12" t="s">
-        <v>33</v>
-      </c>
+      <c r="F34" s="34"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="12"/>
+      <c r="P34" s="12"/>
+      <c r="Q34" s="12"/>
       <c r="R34" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T34" s="35"/>
-      <c r="U34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V34" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="T34" s="34"/>
+      <c r="U34" s="12"/>
+      <c r="V34" s="36"/>
       <c r="W34" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X34" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y34" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z34" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AA34" s="35"/>
+      <c r="AA34" s="34"/>
       <c r="AB34" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC34" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD34" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE34" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AF34" s="12"/>
-      <c r="AG34" s="12"/>
-      <c r="AH34" s="35"/>
-      <c r="AI34" s="12"/>
+      <c r="AF34" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG34" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH34" s="34"/>
+      <c r="AI34" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ34" s="5">
-        <f>COUNTIF(F34:AI34,"P")</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="AK34" s="5">
-        <f>COUNTIF(F34:AI34,"A")</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A35" s="13">
-        <v>30</v>
+      <c r="A35" s="6">
+        <v>31</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="16" t="s">
-        <v>127</v>
+        <v>27</v>
       </c>
       <c r="D35" s="17"/>
       <c r="E35" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F35" s="35"/>
+      <c r="F35" s="34"/>
       <c r="G35" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J35" s="12" t="s">
         <v>32</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M35" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="M35" s="34"/>
       <c r="N35" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O35" s="12" t="s">
         <v>32</v>
@@ -7532,316 +7916,161 @@
         <v>32</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R35" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S35" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T35" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="T35" s="34"/>
       <c r="U35" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V35" s="37"/>
+        <v>32</v>
+      </c>
+      <c r="V35" s="36"/>
       <c r="W35" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X35" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y35" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z35" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA35" s="35"/>
+        <v>31</v>
+      </c>
+      <c r="AA35" s="34"/>
       <c r="AB35" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC35" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD35" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE35" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF35" s="12"/>
-      <c r="AG35" s="12"/>
-      <c r="AH35" s="35"/>
-      <c r="AI35" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF35" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG35" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH35" s="34"/>
+      <c r="AI35" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ35" s="5">
-        <f>COUNTIF(F35:AI35,"P")</f>
-        <v>18</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="AK35" s="5">
-        <f>COUNTIF(F35:AI35,"A")</f>
-        <v>3</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
-        <v>31</v>
+      <c r="A36" s="13">
+        <v>32</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>31</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="D36" s="17"/>
       <c r="E36" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="35"/>
+      <c r="F36" s="34"/>
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
       <c r="K36" s="12"/>
       <c r="L36" s="12"/>
-      <c r="M36" s="35"/>
+      <c r="M36" s="34"/>
       <c r="N36" s="12"/>
       <c r="O36" s="12"/>
       <c r="P36" s="12"/>
       <c r="Q36" s="12"/>
-      <c r="R36" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="S36" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T36" s="35"/>
+      <c r="R36" s="12"/>
+      <c r="S36" s="12"/>
+      <c r="T36" s="34"/>
       <c r="U36" s="12"/>
-      <c r="V36" s="37"/>
+      <c r="V36" s="36"/>
       <c r="W36" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X36" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y36" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z36" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA36" s="35"/>
+        <v>32</v>
+      </c>
+      <c r="AA36" s="34"/>
       <c r="AB36" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC36" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD36" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE36" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF36" s="12"/>
-      <c r="AG36" s="12"/>
-      <c r="AH36" s="35"/>
-      <c r="AI36" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="AF36" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG36" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH36" s="34"/>
+      <c r="AI36" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="AJ36" s="5">
-        <f>COUNTIF(F36:AI36,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="AK36" s="5">
-        <f>COUNTIF(F36:AI36,"A")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A37" s="13">
-        <v>32</v>
-      </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="17"/>
-      <c r="E37" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="35"/>
-      <c r="G37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="L37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M37" s="35"/>
-      <c r="N37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="P37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="R37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="S37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T37" s="35"/>
-      <c r="U37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V37" s="37"/>
-      <c r="W37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="X37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z37" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA37" s="35"/>
-      <c r="AB37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF37" s="12"/>
-      <c r="AG37" s="12"/>
-      <c r="AH37" s="35"/>
-      <c r="AI37" s="12"/>
-      <c r="AJ37" s="5">
-        <f>COUNTIF(F37:AI37,"P")</f>
-        <v>20</v>
-      </c>
-      <c r="AK37" s="5">
-        <f>COUNTIF(F37:AI37,"A")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
-        <v>33</v>
-      </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="D38" s="17"/>
-      <c r="E38" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="35"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
-      <c r="M38" s="35"/>
-      <c r="N38" s="12"/>
-      <c r="O38" s="12"/>
-      <c r="P38" s="12"/>
-      <c r="Q38" s="12"/>
-      <c r="R38" s="12"/>
-      <c r="S38" s="12"/>
-      <c r="T38" s="35"/>
-      <c r="U38" s="12"/>
-      <c r="V38" s="37"/>
-      <c r="W38" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="X38" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y38" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z38" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA38" s="35"/>
-      <c r="AB38" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC38" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD38" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE38" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF38" s="12"/>
-      <c r="AG38" s="12"/>
-      <c r="AH38" s="35"/>
-      <c r="AI38" s="12"/>
-      <c r="AJ38" s="5">
-        <f>COUNTIF(F38:AI38,"P")</f>
-        <v>8</v>
-      </c>
-      <c r="AK38" s="5">
-        <f>COUNTIF(F38:AI38,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="AJ4:AJ5"/>
-    <mergeCell ref="AK4:AK5"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="F6:F38"/>
-    <mergeCell ref="M6:M38"/>
-    <mergeCell ref="T6:T38"/>
-    <mergeCell ref="V6:V38"/>
-    <mergeCell ref="AA6:AA38"/>
-    <mergeCell ref="AH6:AH38"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:U3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
+  <mergeCells count="16">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="A2:AI2"/>
+    <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="F5:F36"/>
+    <mergeCell ref="M5:M36"/>
+    <mergeCell ref="T5:T36"/>
+    <mergeCell ref="V5:V36"/>
+    <mergeCell ref="AA5:AA36"/>
+    <mergeCell ref="AH5:AH36"/>
   </mergeCells>
-  <conditionalFormatting sqref="F6 M6 T6 V6 AA6 AH6 F5:AI5 U6:U38 AI6:AI38 G6:L38 N6:S38 W6:Z38 AB6:AG38">
+  <conditionalFormatting sqref="F5 M5 T5 V5 AA5 AH5 F4:AI4 G5:L36 N5:S36 U5:U36 W5:Z36 AB5:AG36 AI5:AI36">
     <cfRule type="expression" dxfId="6" priority="8">
-      <formula>IF(F$5=TODAY(),TRUE,FALSE)</formula>
+      <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6 M6 T6 V6 AA6 AH6 U6:U38 AI6:AI38 G6:L38 N6:S38 W6:Z38 AB6:AG38">
+  <conditionalFormatting sqref="F5 M5 T5 V5 AA5 AH5 G5:L36 N5:S36 U5:U36 W5:Z36 AB5:AG36 AI5:AI36">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"A"</formula>
     </cfRule>
@@ -7849,23 +8078,23 @@
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6 M6 T6 V6 AA6 AH6 F4:AI5 U6:U38 AI6:AI38 G6:L38 N6:S38 W6:Z38 AB6:AG38">
+  <conditionalFormatting sqref="F3:AI4 F5 M5 T5 V5 AA5 AH5 G5:L36 N5:S36 U5:U36 W5:Z36 AB5:AG36 AI5:AI36">
     <cfRule type="expression" dxfId="3" priority="9">
-      <formula>F$4="Sun"</formula>
+      <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ4:AK4 AJ6:AK38">
+  <conditionalFormatting sqref="AJ3:AK3 AJ5:AK36">
     <cfRule type="expression" dxfId="2" priority="10">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL8:AM8 AL9:AL10 AL13:AL16 AL21:AL24 AM13:AO13 AM21:AO21">
+  <conditionalFormatting sqref="AL7:AM7 AL8:AL9 AM19:AO19 AL19:AL22 AL12:AL14">
     <cfRule type="expression" dxfId="1" priority="73">
-      <formula>AL$7="Sun"</formula>
+      <formula>AL$6="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6:B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="124"/>
+  <conditionalFormatting sqref="B5:B36">
+    <cfRule type="duplicateValues" dxfId="0" priority="125"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
